--- a/data/WP17_auswertung_abgeordnete.xlsx
+++ b/data/WP17_auswertung_abgeordnete.xlsx
@@ -3088,13 +3088,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{97BEA853-EAE4-4B4F-AFA0-B771C26DDFA1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19C08453-EAD1-4D97-AF95-172B69A9BDA3}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{67F99A33-1C31-4407-BC53-E2338B4C2673}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4516DF05-B7F5-4B12-9A98-3FB5B9BFD668}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{92E2D1DD-0A5F-4D81-A753-E89374135865}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2143520A-0C9A-49C4-A1F8-8B4D8AB98AEB}"/>
 </file>